--- a/tools/importer/reports/import-car-insurance.report.xlsx
+++ b/tools/importer/reports/import-car-insurance.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
   <si>
     <t>_reportFile</t>
   </si>
@@ -64,7 +64,7 @@
     <t>car-insurance/faqs.report.json</t>
   </si>
   <si>
-    <t>["hero-overlay","anchor-nav","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","form","carousel-product"]</t>
+    <t>["hero-overlay","anchor-nav","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","accordion-faq","form"]</t>
   </si>
   <si>
     <t>car-insurance/faqs</t>
@@ -73,13 +73,229 @@
     <t>car-insurance</t>
   </si>
   <si>
-    <t>2026-09-14T16:02:34.345Z</t>
+    <t>2026-09-23T15:02:05.265Z</t>
   </si>
   <si>
     <t>Frequently Asked Questions | Saga Car Insurance</t>
   </si>
   <si>
     <t>https://www.saga.co.uk/car-insurance/faqs</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/daily-habits-to-keep-liver-healthy.report.json</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/daily-habits-to-keep-liver-healthy</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:21:12.329Z</t>
+  </si>
+  <si>
+    <t>How to keep your liver healthy: 7 daily habits from the medical experts</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/health-and-wellbeing/daily-habits-to-keep-liver-healthy</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/food-combinations-you-should-avoid.report.json</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/food-combinations-you-should-avoid</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:19:58.991Z</t>
+  </si>
+  <si>
+    <t>6 food combinations you should avoid – and what to eat instead</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/health-and-wellbeing/food-combinations-you-should-avoid</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/foods-you-should-wash.report.json</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/foods-you-should-wash</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:22:56.689Z</t>
+  </si>
+  <si>
+    <t>Foods you should wash – and those you shouldn’t</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/health-and-wellbeing/foods-you-should-wash</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/hot-drinks-and-cancer.report.json</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/hot-drinks-and-cancer</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:20:15.703Z</t>
+  </si>
+  <si>
+    <t>Tea, coffee and cancer risk: how hot is too hot?</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/health-and-wellbeing/hot-drinks-and-cancer</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/how-early-is-too-early-to-wake-up.report.json</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/how-early-is-too-early-to-wake-up</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:21:25.371Z</t>
+  </si>
+  <si>
+    <t>How early is too early to wake up</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/health-and-wellbeing/how-early-is-too-early-to-wake-up</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/meat-free-alternatives-best-for-health.report.json</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/meat-free-alternatives-best-for-health</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:23:09.522Z</t>
+  </si>
+  <si>
+    <t>Which meat-free alternatives are best for your health?</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/health-and-wellbeing/meat-free-alternatives-best-for-health</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/shingles-vaccine-over-80s.report.json</t>
+  </si>
+  <si>
+    <t>magazine/health-and-wellbeing/shingles-vaccine-over-80s</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:23:25.132Z</t>
+  </si>
+  <si>
+    <t>Why can’t over-80s get the shingles vaccine?</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/health-and-wellbeing/shingles-vaccine-over-80s</t>
+  </si>
+  <si>
+    <t>magazine/homes/air-fryer-hacks-to-get-the-best-cooking-results.report.json</t>
+  </si>
+  <si>
+    <t>magazine/homes/air-fryer-hacks-to-get-the-best-cooking-results</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:25:01.259Z</t>
+  </si>
+  <si>
+    <t>8 air fryer hacks to get the best cooking results</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/homes/air-fryer-hacks-to-get-the-best-cooking-results</t>
+  </si>
+  <si>
+    <t>magazine/homes/foods-you-must-never-store-together.report.json</t>
+  </si>
+  <si>
+    <t>magazine/homes/foods-you-must-never-store-together</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:26:07.693Z</t>
+  </si>
+  <si>
+    <t>The foods you must never store together</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/homes/foods-you-must-never-store-together</t>
+  </si>
+  <si>
+    <t>magazine/homes/how-to-keep-flies-out-of-the-house.report.json</t>
+  </si>
+  <si>
+    <t>magazine/homes/how-to-keep-flies-out-of-the-house</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:25:56.719Z</t>
+  </si>
+  <si>
+    <t>How to keep flies out of the house</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/homes/how-to-keep-flies-out-of-the-house</t>
+  </si>
+  <si>
+    <t>magazine/life/dr-miriam-retirement-driving-a-wedge.report.json</t>
+  </si>
+  <si>
+    <t>magazine/life/dr-miriam-retirement-driving-a-wedge</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:21:59.472Z</t>
+  </si>
+  <si>
+    <t>Dr miriam retirement driving a wedge</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/life/dr-miriam-retirement-driving-a-wedge</t>
+  </si>
+  <si>
+    <t>magazine/life/health-benefits-of-pets.report.json</t>
+  </si>
+  <si>
+    <t>magazine/life/health-benefits-of-pets</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:23:51.482Z</t>
+  </si>
+  <si>
+    <t>5 surprising health benefits of owning a dog or cat</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/life/health-benefits-of-pets</t>
+  </si>
+  <si>
+    <t>magazine/life/susie-dent-words-for-weather.report.json</t>
+  </si>
+  <si>
+    <t>magazine/life/susie-dent-words-for-weather</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:24:04.404Z</t>
+  </si>
+  <si>
+    <t>Susie Dent on words for the weather</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/life/susie-dent-words-for-weather</t>
+  </si>
+  <si>
+    <t>magazine/life/why-britain-loves-benches.report.json</t>
+  </si>
+  <si>
+    <t>magazine/life/why-britain-loves-benches</t>
+  </si>
+  <si>
+    <t>2026-09-22T14:23:39.025Z</t>
+  </si>
+  <si>
+    <t>Why Britain's love affair with benches shows no sign of fading</t>
+  </si>
+  <si>
+    <t>https://www.saga.co.uk/magazine/life/why-britain-loves-benches</t>
   </si>
 </sst>
 </file>
@@ -468,16 +684,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="1" max="3" width="50" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="43" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -556,6 +769,370 @@
       </c>
       <c r="H3" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>80</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
